--- a/test_data/Orion_Stress_Demo/PN-BETA-02/40202/BU02/HRM/post DDV_HRM-2031-0440/Panel 7/Coupon back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU02_Coupon_Back_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-BETA-02/40202/BU02/HRM/post DDV_HRM-2031-0440/Panel 7/Coupon back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU02_Coupon_Back_Summary.xlsx
@@ -460,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16.78304</v>
+        <v>16.80351</v>
       </c>
       <c r="D2" t="n">
-        <v>16.79301</v>
+        <v>16.48922</v>
       </c>
       <c r="E2" t="n">
-        <v>17.11333</v>
+        <v>16.56885</v>
       </c>
       <c r="F2" t="n">
-        <v>42.36715</v>
+        <v>42.98571</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0508</v>
+        <v>0.0506</v>
       </c>
       <c r="H2" t="n">
-        <v>1.81026</v>
+        <v>1.77825</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16.54867</v>
+        <v>17.07827</v>
       </c>
       <c r="D3" t="n">
-        <v>16.60978</v>
+        <v>16.51501</v>
       </c>
       <c r="E3" t="n">
-        <v>16.5171</v>
+        <v>16.57859</v>
       </c>
       <c r="F3" t="n">
-        <v>41.91842</v>
+        <v>42.18277</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05059</v>
+        <v>0.05025</v>
       </c>
       <c r="H3" t="n">
-        <v>1.85407</v>
+        <v>1.80294</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16.56248</v>
+        <v>16.98649</v>
       </c>
       <c r="D4" t="n">
-        <v>16.51821</v>
+        <v>16.38707</v>
       </c>
       <c r="E4" t="n">
-        <v>16.67277</v>
+        <v>16.74191</v>
       </c>
       <c r="F4" t="n">
-        <v>42.71624</v>
+        <v>41.76265</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05097</v>
+        <v>0.05183</v>
       </c>
       <c r="H4" t="n">
-        <v>1.81938</v>
+        <v>1.77507</v>
       </c>
     </row>
     <row r="5">
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16.67587</v>
+        <v>16.77747</v>
       </c>
       <c r="D6" t="n">
-        <v>16.09138</v>
+        <v>15.78303</v>
       </c>
       <c r="E6" t="n">
-        <v>16.79778</v>
+        <v>16.49646</v>
       </c>
       <c r="F6" t="n">
-        <v>21.74581</v>
+        <v>21.88014</v>
       </c>
       <c r="G6" t="n">
-        <v>34.50701</v>
+        <v>34.57745</v>
       </c>
     </row>
     <row r="7">
@@ -589,19 +589,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16.54802</v>
+        <v>16.48909</v>
       </c>
       <c r="D7" t="n">
-        <v>16.17237</v>
+        <v>16.23452</v>
       </c>
       <c r="E7" t="n">
-        <v>16.82056</v>
+        <v>16.36892</v>
       </c>
       <c r="F7" t="n">
-        <v>22.29007</v>
+        <v>22.00879</v>
       </c>
       <c r="G7" t="n">
-        <v>34.03287</v>
+        <v>33.7918</v>
       </c>
     </row>
     <row r="8">
@@ -611,19 +611,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.70478</v>
+        <v>17.13369</v>
       </c>
       <c r="D8" t="n">
-        <v>15.95965</v>
+        <v>15.70537</v>
       </c>
       <c r="E8" t="n">
-        <v>16.34492</v>
+        <v>16.374</v>
       </c>
       <c r="F8" t="n">
-        <v>21.79831</v>
+        <v>21.64726</v>
       </c>
       <c r="G8" t="n">
-        <v>34.02531</v>
+        <v>34.02326</v>
       </c>
     </row>
   </sheetData>
